--- a/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · La tragedia del duque de Berganza</t>
   </si>
   <si>
-    <t>Para María Rosa Álvarez Sellers · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para María Rosa Álvarez Sellers · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>
@@ -123,7 +123,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 13 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 13 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t/>
@@ -141,7 +141,7 @@
     <t>Redondilla · Octosílaba</t>
   </si>
   <si>
-    <t>Solo tiene 2 versos, y «Octosílaba» necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
+    <t>Solo tiene 2 versos, y una redondilla octosílaba necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
   </si>
   <si>
     <t>L|41a84c24-6f43-493b-8982-56f17523cda4</t>
@@ -288,7 +288,7 @@
     <t>Octosílabo</t>
   </si>
   <si>
-    <t>Revisar: Tiene 13 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Revisar: Tiene 13 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>1 derivada</t>
@@ -297,7 +297,7 @@
     <t>rasgo</t>
   </si>
   <si>
-    <t>Revisar: Solo tiene 2 versos, y «Octosílaba» necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
+    <t>Revisar: Solo tiene 2 versos, y una redondilla octosílaba necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
   </si>
 </sst>
 </file>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -231,7 +231,7 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
+    <t>Sílabas del verso</t>
   </si>
   <si>
     <t>#</t>
@@ -1208,7 +1208,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>Migración métrica · La tragedia del duque de Berganza</t>
   </si>
   <si>
-    <t>Para María Rosa Álvarez Sellers · generado el 2026-09-20</t>
+    <t>Para María Rosa Álvarez Sellers · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
@@ -123,7 +123,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 13 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 13 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t/>
@@ -141,7 +141,7 @@
     <t>Redondilla · Octosílaba</t>
   </si>
   <si>
-    <t>Solo tiene 2 versos, y una redondilla octosílaba necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
+    <t>Solo tiene 2 versos, y una redondilla octosílaba necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma. Hasta saber esto no te pregunto nada más de este pasaje.</t>
   </si>
   <si>
     <t>L|41a84c24-6f43-493b-8982-56f17523cda4</t>
@@ -171,31 +171,25 @@
     <t>R|1db4c67d-051e-4270-b4ff-0259cd2111ae|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
   </si>
   <si>
+    <t>Pregunta</t>
+  </si>
+  <si>
+    <t>Vocabulario anterior</t>
+  </si>
+  <si>
+    <t>¿Correcto?</t>
+  </si>
+  <si>
+    <t>Corrección</t>
+  </si>
+  <si>
+    <t>65–128</t>
+  </si>
+  <si>
+    <t>Octava real · Endecasílaba consonante</t>
+  </si>
+  <si>
     <t>Esquema de rima</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>R|41a84c24-6f43-493b-8982-56f17523cda4|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>Pregunta</t>
-  </si>
-  <si>
-    <t>Vocabulario anterior</t>
-  </si>
-  <si>
-    <t>¿Correcto?</t>
-  </si>
-  <si>
-    <t>Corrección</t>
-  </si>
-  <si>
-    <t>65–128</t>
-  </si>
-  <si>
-    <t>Octava real · Endecasílaba consonante</t>
   </si>
   <si>
     <t>ABABABCC en las 8 estrofas</t>
@@ -858,7 +852,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1032,38 +1026,6 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="3">
@@ -1073,7 +1035,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G3">
       <formula1>Listas!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G6">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G5">
       <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1106,19 +1068,19 @@
         <v>24</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>30</v>
@@ -1129,31 +1091,31 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1164,25 +1126,25 @@
         <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1222,22 +1184,22 @@
         <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="H1" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>30</v>
@@ -1273,37 +1235,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>26</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1317,28 +1279,28 @@
         <v>64</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1346,34 +1308,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3">
         <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1387,28 +1349,28 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1422,28 +1384,28 @@
         <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1457,28 +1419,28 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="94">
   <si>
     <t>Migración métrica · La tragedia del duque de Berganza</t>
   </si>
@@ -123,7 +123,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 13 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Tiene 13 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t/>
@@ -141,7 +141,7 @@
     <t>Redondilla · Octosílaba</t>
   </si>
   <si>
-    <t>Solo tiene 2 versos, y una redondilla octosílaba necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma. Hasta saber esto no te pregunto nada más de este pasaje.</t>
+    <t>Solo tiene 2 versos, y una redondilla octosílaba necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma. Lo demás que te pregunto de este pasaje va contestado de una vez para todas sus estrofas, así que la respuesta vale igual si el rango cambia.</t>
   </si>
   <si>
     <t>L|41a84c24-6f43-493b-8982-56f17523cda4</t>
@@ -171,6 +171,15 @@
     <t>R|1db4c67d-051e-4270-b4ff-0259cd2111ae|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
   </si>
   <si>
+    <t>Esquema de rima</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable. Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+  </si>
+  <si>
+    <t>R|41a84c24-6f43-493b-8982-56f17523cda4|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
     <t>Pregunta</t>
   </si>
   <si>
@@ -187,9 +196,6 @@
   </si>
   <si>
     <t>Octava real · Endecasílaba consonante</t>
-  </si>
-  <si>
-    <t>Esquema de rima</t>
   </si>
   <si>
     <t>ABABABCC en las 8 estrofas</t>
@@ -852,7 +858,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1026,6 +1032,38 @@
         <v>50</v>
       </c>
     </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="3">
@@ -1035,7 +1073,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G3">
       <formula1>Listas!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G6">
       <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1068,19 +1106,19 @@
         <v>24</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>30</v>
@@ -1091,19 +1129,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>36</v>
@@ -1115,7 +1153,7 @@
         <v>36</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1126,13 +1164,13 @@
         <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>36</v>
@@ -1144,7 +1182,7 @@
         <v>36</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1184,22 +1222,22 @@
         <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>30</v>
@@ -1235,37 +1273,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>26</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1279,28 +1317,28 @@
         <v>64</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1308,34 +1346,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3">
         <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1349,28 +1387,28 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1384,28 +1422,28 @@
         <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1419,28 +1457,28 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -156,7 +156,7 @@
     <t>Esquema de rima · 16 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta)</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
   </si>
   <si>
     <t>R|854d52fa-5d57-40ea-ac33-4bef0dd96970|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-tragedia-del-duque-de-berganza.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="89">
   <si>
     <t>Migración métrica · La tragedia del duque de Berganza</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -42,21 +42,6 @@
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
-  </si>
-  <si>
     <t>lista</t>
   </si>
   <si>
@@ -156,7 +141,7 @@
     <t>Esquema de rima · 16 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab»</t>
   </si>
   <si>
     <t>R|854d52fa-5d57-40ea-ac33-4bef0dd96970|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -362,14 +347,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -718,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -762,31 +746,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -805,49 +764,49 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -872,196 +831,196 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1098,91 +1057,91 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>31</v>
+      <c r="E1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1214,36 +1173,36 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>31</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1271,39 +1230,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1311,34 +1270,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3">
         <v>64</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1346,34 +1305,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3">
         <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1381,34 +1340,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3">
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1416,34 +1375,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3">
         <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1451,34 +1410,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3">
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
